--- a/Assets/@Resources/Data/Excel/ScriptData.xlsx
+++ b/Assets/@Resources/Data/Excel/ScriptData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\stopresent\Unity\RE001\Assets\@Resources\Data\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{E734707A-DA02-47A0-AF01-18F46BB23A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B07C181-5AB6-44F8-91BC-EDAC97ED7549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{68FFC844-373B-4BEC-B5EC-BC8B329811A3}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{68FFC844-373B-4BEC-B5EC-BC8B329811A3}"/>
   </bookViews>
   <sheets>
     <sheet name="ScriptData" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
     <t>Id</t>
   </si>
@@ -35,6 +35,28 @@
   </si>
   <si>
     <t>Ch</t>
+  </si>
+  <si>
+    <t>테스트</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>test</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>여정</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>[&lt;#2DFF00&gt;&lt;b&gt;여정&lt;/b&gt;&lt;/color&gt;]이 해금되었습니다.
+&lt;size=10&gt;이제 소유한 통행증의 허가 범위 내 
+알게 된 모든 장소들로 자유로운 
+이동이 가능해 졌습니다.&lt;/size&gt;</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>journey</t>
   </si>
 </sst>
 </file>
@@ -627,8 +649,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1006,10 +1031,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2548767C-A124-4787-80DD-3672E00ADB84}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1024,6 +1049,39 @@
       </c>
       <c r="E1" t="s">
         <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="A2">
+        <v>1000</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.6">
+      <c r="A3">
+        <v>10001</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="1">
+        <v>10002</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
